--- a/apps/typescript/hirecall/public/samples/candidates.sample.xlsx
+++ b/apps/typescript/hirecall/public/samples/candidates.sample.xlsx
@@ -596,7 +596,7 @@
         <v>yes</v>
       </c>
       <c r="C3" t="str">
-        <v>Mobile with country code. Examples: +14155550123 or +14155550123. No spaces.</v>
+        <v>Mobile with country code. Example reserved number: +14155550123. Replace with a real E.164 number before live calls.</v>
       </c>
       <c r="D3" t="str">
         <v>+14155550123</v>
